--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1067">
   <si>
     <t>KK Girder Project</t>
   </si>
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sat Sep 12 2026 09:59:01</t>
+    <t>Date: Sun Sep 13 2026 09:59:01</t>
   </si>
   <si>
     <t/>
@@ -2725,6 +2725,9 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
+    <t>118 Nos</t>
+  </si>
+  <si>
     <t>Sunction Pipe 1.5in</t>
   </si>
   <si>
@@ -3019,7 +3022,7 @@
     <t>Wedges 0.5"</t>
   </si>
   <si>
-    <t>1639 Nos</t>
+    <t>3339 Nos</t>
   </si>
   <si>
     <t>Weight Scale 100Kg</t>
@@ -13547,7 +13550,7 @@
         <v>9</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>132</v>
+        <v>904</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
@@ -13555,13 +13558,13 @@
         <v>707</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C712" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
@@ -13569,7 +13572,7 @@
         <v>708</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>9</v>
@@ -13583,7 +13586,7 @@
         <v>709</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>9</v>
@@ -13597,7 +13600,7 @@
         <v>710</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>9</v>
@@ -13611,7 +13614,7 @@
         <v>711</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>9</v>
@@ -13625,13 +13628,13 @@
         <v>712</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C717" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
@@ -13639,7 +13642,7 @@
         <v>713</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>9</v>
@@ -13653,7 +13656,7 @@
         <v>714</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>9</v>
@@ -13667,7 +13670,7 @@
         <v>715</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>9</v>
@@ -13681,7 +13684,7 @@
         <v>716</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>9</v>
@@ -13695,13 +13698,13 @@
         <v>717</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
@@ -13709,13 +13712,13 @@
         <v>718</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
@@ -13723,13 +13726,13 @@
         <v>719</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
@@ -13737,7 +13740,7 @@
         <v>720</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>9</v>
@@ -13751,13 +13754,13 @@
         <v>721</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
@@ -13765,13 +13768,13 @@
         <v>722</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D727" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
@@ -13779,13 +13782,13 @@
         <v>723</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C728" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D728" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
@@ -13793,13 +13796,13 @@
         <v>724</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D729" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
@@ -13807,13 +13810,13 @@
         <v>725</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D730" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
@@ -13821,7 +13824,7 @@
         <v>726</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>9</v>
@@ -13835,7 +13838,7 @@
         <v>727</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>9</v>
@@ -13849,7 +13852,7 @@
         <v>728</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>9</v>
@@ -13863,13 +13866,13 @@
         <v>729</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C734" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D734" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
@@ -13877,7 +13880,7 @@
         <v>730</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>9</v>
@@ -13891,13 +13894,13 @@
         <v>731</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D736" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
@@ -13905,7 +13908,7 @@
         <v>732</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>9</v>
@@ -13919,7 +13922,7 @@
         <v>733</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>9</v>
@@ -13933,7 +13936,7 @@
         <v>734</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>9</v>
@@ -13947,7 +13950,7 @@
         <v>735</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>9</v>
@@ -13961,7 +13964,7 @@
         <v>736</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>9</v>
@@ -13975,7 +13978,7 @@
         <v>737</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>9</v>
@@ -13989,7 +13992,7 @@
         <v>738</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>9</v>
@@ -14003,7 +14006,7 @@
         <v>739</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>9</v>
@@ -14017,7 +14020,7 @@
         <v>740</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>9</v>
@@ -14031,7 +14034,7 @@
         <v>741</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>9</v>
@@ -14045,7 +14048,7 @@
         <v>742</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>9</v>
@@ -14059,7 +14062,7 @@
         <v>743</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>9</v>
@@ -14073,7 +14076,7 @@
         <v>744</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>9</v>
@@ -14087,7 +14090,7 @@
         <v>745</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>9</v>
@@ -14101,7 +14104,7 @@
         <v>746</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>9</v>
@@ -14115,7 +14118,7 @@
         <v>747</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>9</v>
@@ -14129,7 +14132,7 @@
         <v>748</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>9</v>
@@ -14143,7 +14146,7 @@
         <v>749</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>9</v>
@@ -14157,7 +14160,7 @@
         <v>750</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>9</v>
@@ -14171,7 +14174,7 @@
         <v>751</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>9</v>
@@ -14185,7 +14188,7 @@
         <v>752</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>9</v>
@@ -14199,7 +14202,7 @@
         <v>753</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>9</v>
@@ -14213,7 +14216,7 @@
         <v>754</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>9</v>
@@ -14227,13 +14230,13 @@
         <v>755</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D760" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
@@ -14241,7 +14244,7 @@
         <v>756</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>9</v>
@@ -14255,13 +14258,13 @@
         <v>757</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D762" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
@@ -14269,13 +14272,13 @@
         <v>758</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D763" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
@@ -14283,7 +14286,7 @@
         <v>759</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>9</v>
@@ -14297,13 +14300,13 @@
         <v>760</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D765" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
@@ -14311,7 +14314,7 @@
         <v>761</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>9</v>
@@ -14325,7 +14328,7 @@
         <v>762</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>9</v>
@@ -14339,7 +14342,7 @@
         <v>763</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>9</v>
@@ -14353,13 +14356,13 @@
         <v>764</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
@@ -14367,7 +14370,7 @@
         <v>765</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>9</v>
@@ -14381,7 +14384,7 @@
         <v>766</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>9</v>
@@ -14395,7 +14398,7 @@
         <v>767</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>9</v>
@@ -14409,7 +14412,7 @@
         <v>768</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>9</v>
@@ -14423,7 +14426,7 @@
         <v>769</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>9</v>
@@ -14437,7 +14440,7 @@
         <v>770</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>9</v>
@@ -14451,7 +14454,7 @@
         <v>771</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>9</v>
@@ -14465,7 +14468,7 @@
         <v>772</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>9</v>
@@ -14479,7 +14482,7 @@
         <v>773</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>9</v>
@@ -14493,7 +14496,7 @@
         <v>774</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>9</v>
@@ -14507,7 +14510,7 @@
         <v>775</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>9</v>
@@ -14521,7 +14524,7 @@
         <v>776</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>9</v>
@@ -14535,7 +14538,7 @@
         <v>777</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>9</v>
@@ -14549,13 +14552,13 @@
         <v>778</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.25">
@@ -14563,13 +14566,13 @@
         <v>779</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D784" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.25">
@@ -14577,7 +14580,7 @@
         <v>780</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>9</v>
@@ -14591,7 +14594,7 @@
         <v>781</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>9</v>
@@ -14605,7 +14608,7 @@
         <v>782</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>9</v>
@@ -14619,7 +14622,7 @@
         <v>783</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>9</v>
@@ -14633,7 +14636,7 @@
         <v>784</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>9</v>
@@ -14647,7 +14650,7 @@
         <v>785</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>9</v>
@@ -14661,13 +14664,13 @@
         <v>786</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.25">
@@ -14675,7 +14678,7 @@
         <v>787</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>9</v>
@@ -14689,7 +14692,7 @@
         <v>788</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>9</v>
@@ -14703,7 +14706,7 @@
         <v>789</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>9</v>
@@ -14717,7 +14720,7 @@
         <v>790</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>9</v>
@@ -14731,7 +14734,7 @@
         <v>791</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>9</v>
@@ -14745,7 +14748,7 @@
         <v>792</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>9</v>
@@ -14759,7 +14762,7 @@
         <v>793</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>9</v>
@@ -14773,7 +14776,7 @@
         <v>794</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>9</v>
@@ -14787,7 +14790,7 @@
         <v>795</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>9</v>
@@ -14801,13 +14804,13 @@
         <v>796</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D801" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.25">
@@ -14815,7 +14818,7 @@
         <v>797</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>9</v>
@@ -14829,7 +14832,7 @@
         <v>798</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>9</v>
@@ -14843,7 +14846,7 @@
         <v>799</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>9</v>
@@ -14857,13 +14860,13 @@
         <v>800</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.25">
@@ -14871,13 +14874,13 @@
         <v>801</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D806" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.25">
@@ -14885,13 +14888,13 @@
         <v>802</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.25">
@@ -14899,13 +14902,13 @@
         <v>803</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D808" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.25">
@@ -14913,13 +14916,13 @@
         <v>804</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.25">
@@ -14927,7 +14930,7 @@
         <v>805</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>9</v>
@@ -14941,7 +14944,7 @@
         <v>806</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>9</v>
@@ -14955,7 +14958,7 @@
         <v>807</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>9</v>
@@ -14969,7 +14972,7 @@
         <v>808</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>9</v>
@@ -14983,7 +14986,7 @@
         <v>809</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>9</v>
@@ -14997,7 +15000,7 @@
         <v>810</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>9</v>
@@ -15011,7 +15014,7 @@
         <v>811</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>9</v>
@@ -15025,7 +15028,7 @@
         <v>812</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>9</v>
@@ -15039,7 +15042,7 @@
         <v>813</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>9</v>
@@ -15053,13 +15056,13 @@
         <v>814</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C819" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D819" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
@@ -15067,13 +15070,13 @@
         <v>815</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C820" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
@@ -15081,13 +15084,13 @@
         <v>816</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C821" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
@@ -15095,7 +15098,7 @@
         <v>817</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>9</v>
@@ -15109,7 +15112,7 @@
         <v>818</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>9</v>
@@ -15123,7 +15126,7 @@
         <v>819</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C824" s="2" t="s">
         <v>9</v>
@@ -15137,7 +15140,7 @@
         <v>820</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>9</v>
@@ -15151,7 +15154,7 @@
         <v>821</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C826" s="2" t="s">
         <v>9</v>
@@ -15165,7 +15168,7 @@
         <v>822</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>9</v>
@@ -15179,13 +15182,13 @@
         <v>823</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C828" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.25">
@@ -15193,13 +15196,13 @@
         <v>824</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D829" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
@@ -15207,13 +15210,13 @@
         <v>825</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
@@ -15221,7 +15224,7 @@
         <v>826</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>9</v>
@@ -15235,7 +15238,7 @@
         <v>827</v>
       </c>
       <c r="B832" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>9</v>
@@ -15249,7 +15252,7 @@
         <v>828</v>
       </c>
       <c r="B833" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C833" s="2" t="s">
         <v>9</v>
@@ -15263,13 +15266,13 @@
         <v>829</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D834" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.25">
@@ -15277,13 +15280,13 @@
         <v>830</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.25">
@@ -15291,13 +15294,13 @@
         <v>831</v>
       </c>
       <c r="B836" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.25">
@@ -15305,13 +15308,13 @@
         <v>832</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.25">
@@ -15319,13 +15322,13 @@
         <v>833</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Sep 13 2026 09:59:01</t>
+    <t>Date: Mon Sep 14 2026 09:59:01</t>
   </si>
   <si>
     <t/>
@@ -220,7 +220,7 @@
     <t>Binding Wire</t>
   </si>
   <si>
-    <t>539 Kg</t>
+    <t>367 Kg</t>
   </si>
   <si>
     <t>Bit 1.5in for Drill Bil</t>
@@ -583,7 +583,7 @@
     <t>Curing Compound Sika Antisol</t>
   </si>
   <si>
-    <t>171 Drum</t>
+    <t>170 Drum</t>
   </si>
   <si>
     <t>Curing Pipe 1in</t>
@@ -871,7 +871,7 @@
     <t>Foam Sheet 5mm</t>
   </si>
   <si>
-    <t>364 Nos</t>
+    <t>354 Nos</t>
   </si>
   <si>
     <t>Folding Pipe 10ft</t>
@@ -1891,7 +1891,7 @@
     <t>PC Strand Wire</t>
   </si>
   <si>
-    <t>446 Roll</t>
+    <t>436 Roll</t>
   </si>
   <si>
     <t>PPR Elbow 25mm</t>
@@ -1999,7 +1999,7 @@
     <t>PVC Pipe 1-1/4"</t>
   </si>
   <si>
-    <t>416 Nos</t>
+    <t>404 Nos</t>
   </si>
   <si>
     <t>PVC Pipe 150mm</t>
@@ -2155,7 +2155,7 @@
     <t>Plastic Saddle</t>
   </si>
   <si>
-    <t>808 Nos</t>
+    <t>793 Nos</t>
   </si>
   <si>
     <t>Platform For Gantry</t>
@@ -2725,487 +2725,487 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
+    <t>98 Nos</t>
+  </si>
+  <si>
+    <t>Sunction Pipe 1.5in</t>
+  </si>
+  <si>
+    <t>1 Rft</t>
+  </si>
+  <si>
+    <t>Surveying Prism</t>
+  </si>
+  <si>
+    <t>Surveying Prism Rod</t>
+  </si>
+  <si>
+    <t>Table Plastic</t>
+  </si>
+  <si>
+    <t>Tea Cup Set</t>
+  </si>
+  <si>
+    <t>Teflon Tape</t>
+  </si>
+  <si>
+    <t>45 Nos</t>
+  </si>
+  <si>
+    <t>Thimble 16/8mm</t>
+  </si>
+  <si>
+    <t>Thimble 35/10mm</t>
+  </si>
+  <si>
+    <t>Thimble 70mm</t>
+  </si>
+  <si>
+    <t>Thimble Press</t>
+  </si>
+  <si>
+    <t>Thinner</t>
+  </si>
+  <si>
+    <t>38 Ltr</t>
+  </si>
+  <si>
+    <t>Through Bolt M16X1000mm</t>
+  </si>
+  <si>
+    <t>240 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M16X900mm</t>
+  </si>
+  <si>
+    <t>860 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M16x900</t>
+  </si>
+  <si>
+    <t>Through Bolt M19X1000mm</t>
+  </si>
+  <si>
+    <t>1005 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M19X1740mm</t>
+  </si>
+  <si>
+    <t>499 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M19X750mm</t>
+  </si>
+  <si>
+    <t>1200 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M19x1750</t>
+  </si>
+  <si>
+    <t>95 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M19x850mm</t>
+  </si>
+  <si>
+    <t>Through Bolt M19x850mm Nut 80Kg</t>
+  </si>
+  <si>
+    <t>Through Bolt M19x850mm Washer 34Kg</t>
+  </si>
+  <si>
+    <t>Through Bolt M20x1350</t>
+  </si>
+  <si>
+    <t>Through Bolt M24X1250mm</t>
+  </si>
+  <si>
+    <t>196 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M24X2300mm</t>
+  </si>
+  <si>
+    <t>Through Bolt M24X850mm</t>
+  </si>
+  <si>
+    <t>330 Nos</t>
+  </si>
+  <si>
+    <t>Through Bolt M30*4000mm</t>
+  </si>
+  <si>
+    <t>Through Bolt M36x1050</t>
+  </si>
+  <si>
+    <t>ThroughBoltM19x700</t>
+  </si>
+  <si>
+    <t>Tieting Machine</t>
+  </si>
+  <si>
+    <t>Toolbox</t>
+  </si>
+  <si>
+    <t>Total Station Machine</t>
+  </si>
+  <si>
+    <t>Tower Cooling</t>
+  </si>
+  <si>
+    <t>Transparent Tape</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 12400mm</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 17.5Ft</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 3.5ft</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 34Ft</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 35Ft</t>
+  </si>
+  <si>
+    <t>Tress For Gantry 600x3800mm</t>
+  </si>
+  <si>
+    <t>Tress For Gantry Jhulla Type</t>
+  </si>
+  <si>
+    <t>Tress For Gantry Small</t>
+  </si>
+  <si>
+    <t>Tress Hook</t>
+  </si>
+  <si>
+    <t>Tripod Stand</t>
+  </si>
+  <si>
+    <t>Troller LWO bed</t>
+  </si>
+  <si>
+    <t>Troller Low Bed</t>
+  </si>
+  <si>
+    <t>Trolley Rehro (Front Part)</t>
+  </si>
+  <si>
+    <t>Trolly Fan</t>
+  </si>
+  <si>
+    <t>Trolly Rehro (front part)</t>
+  </si>
+  <si>
+    <t>Trolly fan 46in</t>
+  </si>
+  <si>
+    <t>4 Set</t>
+  </si>
+  <si>
+    <t>Trowel</t>
+  </si>
+  <si>
+    <t>Trumpet Cone 17/0.5in</t>
+  </si>
+  <si>
+    <t>479 Nos</t>
+  </si>
+  <si>
+    <t>Trumpet Cone 4/0.5in</t>
+  </si>
+  <si>
+    <t>918 Nos</t>
+  </si>
+  <si>
+    <t>Trumpet Large Size</t>
+  </si>
+  <si>
+    <t>Twister Bar</t>
+  </si>
+  <si>
+    <t>90 Nos</t>
+  </si>
+  <si>
+    <t>Tyres and Rims For Welding Generator (Miller)</t>
+  </si>
+  <si>
+    <t>Umbrella Large with Base</t>
+  </si>
+  <si>
+    <t>Underground Valve 25mm</t>
+  </si>
+  <si>
+    <t>Valve 1/2 S.S</t>
+  </si>
+  <si>
+    <t>77 Nos</t>
+  </si>
+  <si>
+    <t>Vibrator Gully</t>
+  </si>
+  <si>
+    <t>Vibrator Motor</t>
+  </si>
+  <si>
+    <t>Vibrator Shaft 50MMx6Mtr</t>
+  </si>
+  <si>
+    <t>Visitor chairs</t>
+  </si>
+  <si>
+    <t>Waher 1.5"X0.5"</t>
+  </si>
+  <si>
+    <t>Warning Tape</t>
+  </si>
+  <si>
+    <t>Washer 20mm</t>
+  </si>
+  <si>
+    <t>Washer 24mm</t>
+  </si>
+  <si>
+    <t>Washer 36mm</t>
+  </si>
+  <si>
+    <t>Washer 3mm</t>
+  </si>
+  <si>
+    <t>Washer 5/8</t>
+  </si>
+  <si>
+    <t>Washer 5mm 3"X3"</t>
+  </si>
+  <si>
+    <t>Washer 6"</t>
+  </si>
+  <si>
+    <t>Washer For T Bolt</t>
+  </si>
+  <si>
+    <t>65 Kg</t>
+  </si>
+  <si>
+    <t>Washer for Dywidag bar</t>
+  </si>
+  <si>
+    <t>23 Nos</t>
+  </si>
+  <si>
+    <t>Washing Machine Haier</t>
+  </si>
+  <si>
+    <t>Water Bowser With Tyres</t>
+  </si>
+  <si>
+    <t>Water Bozzer</t>
+  </si>
+  <si>
+    <t>Water Cooler</t>
+  </si>
+  <si>
+    <t>Water Pump 0.75HP</t>
+  </si>
+  <si>
+    <t>Wax</t>
+  </si>
+  <si>
+    <t>Wedges 0.5"</t>
+  </si>
+  <si>
+    <t>2999 Nos</t>
+  </si>
+  <si>
+    <t>Weight Scale 100Kg</t>
+  </si>
+  <si>
+    <t>Welding Generator (Lincoln)</t>
+  </si>
+  <si>
+    <t>Welding Generator (Miller)</t>
+  </si>
+  <si>
+    <t>Welding Generator Daw-500</t>
+  </si>
+  <si>
+    <t>Welding Generator Lincoln</t>
+  </si>
+  <si>
+    <t>Welding Generator Miller</t>
+  </si>
+  <si>
+    <t>Welding Generator Perkins</t>
+  </si>
+  <si>
+    <t>Welding Glass</t>
+  </si>
+  <si>
+    <t>Welding Gloves</t>
+  </si>
+  <si>
+    <t>Welding Lead</t>
+  </si>
+  <si>
+    <t>20 Rft</t>
+  </si>
+  <si>
+    <t>Welding Plant 3 phase</t>
+  </si>
+  <si>
+    <t>Welding Plant 3Phase 2X400</t>
+  </si>
+  <si>
+    <t>Welding Plant 3Phase 500A with lead</t>
+  </si>
+  <si>
+    <t>Welding Rod 10#</t>
+  </si>
+  <si>
+    <t>80 Pkt</t>
+  </si>
+  <si>
+    <t>Welding Rod 10# (7018)</t>
+  </si>
+  <si>
+    <t>0 Pkt</t>
+  </si>
+  <si>
+    <t>Welding Rod 12#</t>
+  </si>
+  <si>
+    <t>32 Pkt</t>
+  </si>
+  <si>
+    <t>Welding Rod 45&amp;48mm</t>
+  </si>
+  <si>
+    <t>96 Nos</t>
+  </si>
+  <si>
+    <t>Welding Rod 8#</t>
+  </si>
+  <si>
+    <t>10 Pkt</t>
+  </si>
+  <si>
+    <t>Welding Rod Holder 1000A</t>
+  </si>
+  <si>
+    <t>Welding Screen</t>
+  </si>
+  <si>
+    <t>Welding plant single phase</t>
+  </si>
+  <si>
+    <t>Wench</t>
+  </si>
+  <si>
+    <t>Wench Double Drum</t>
+  </si>
+  <si>
+    <t>Wench Roller</t>
+  </si>
+  <si>
+    <t>WiFi USB</t>
+  </si>
+  <si>
+    <t>Wind Pipe</t>
+  </si>
+  <si>
+    <t>Wire Bush</t>
+  </si>
+  <si>
+    <t>Wooden Batten 3inx6inx8ft</t>
+  </si>
+  <si>
+    <t>437 Nos</t>
+  </si>
+  <si>
+    <t>Wooden Batten 4inx8ft</t>
+  </si>
+  <si>
+    <t>269 Nos</t>
+  </si>
+  <si>
+    <t>Wooden Batten 6 1/2ftx1 1/2inx6in</t>
+  </si>
+  <si>
+    <t>70 Nos</t>
+  </si>
+  <si>
+    <t>Wooden Bhatta</t>
+  </si>
+  <si>
+    <t>Wooden Cutting Disc 14"</t>
+  </si>
+  <si>
+    <t>Wooden Garmala</t>
+  </si>
+  <si>
+    <t>Wooden Gutka 18"*18*3ft</t>
+  </si>
+  <si>
+    <t>Wooden Screw 4"</t>
+  </si>
+  <si>
+    <t>Wooden Washers</t>
+  </si>
+  <si>
+    <t>Wooden batten 3"*4"*8ft</t>
+  </si>
+  <si>
+    <t>814 Nos</t>
+  </si>
+  <si>
+    <t>Wooden packen</t>
+  </si>
+  <si>
+    <t>1667 Nos</t>
+  </si>
+  <si>
+    <t>Wooden washer 4"*6"</t>
+  </si>
+  <si>
+    <t>Work Bench Clump 6in</t>
+  </si>
+  <si>
+    <t>Writing pad small</t>
+  </si>
+  <si>
+    <t>pad lock</t>
+  </si>
+  <si>
+    <t>pvc pipe 1inch</t>
+  </si>
+  <si>
+    <t>980 Nos</t>
+  </si>
+  <si>
+    <t>sheet pipe 81mm</t>
+  </si>
+  <si>
+    <t>541 Nos</t>
+  </si>
+  <si>
+    <t>sheet pipe 84mm</t>
+  </si>
+  <si>
     <t>118 Nos</t>
   </si>
   <si>
-    <t>Sunction Pipe 1.5in</t>
-  </si>
-  <si>
-    <t>1 Rft</t>
-  </si>
-  <si>
-    <t>Surveying Prism</t>
-  </si>
-  <si>
-    <t>Surveying Prism Rod</t>
-  </si>
-  <si>
-    <t>Table Plastic</t>
-  </si>
-  <si>
-    <t>Tea Cup Set</t>
-  </si>
-  <si>
-    <t>Teflon Tape</t>
-  </si>
-  <si>
-    <t>45 Nos</t>
-  </si>
-  <si>
-    <t>Thimble 16/8mm</t>
-  </si>
-  <si>
-    <t>Thimble 35/10mm</t>
-  </si>
-  <si>
-    <t>Thimble 70mm</t>
-  </si>
-  <si>
-    <t>Thimble Press</t>
-  </si>
-  <si>
-    <t>Thinner</t>
-  </si>
-  <si>
-    <t>38 Ltr</t>
-  </si>
-  <si>
-    <t>Through Bolt M16X1000mm</t>
-  </si>
-  <si>
-    <t>240 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M16X900mm</t>
-  </si>
-  <si>
-    <t>860 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M16x900</t>
-  </si>
-  <si>
-    <t>Through Bolt M19X1000mm</t>
-  </si>
-  <si>
-    <t>1005 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M19X1740mm</t>
-  </si>
-  <si>
-    <t>499 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M19X750mm</t>
-  </si>
-  <si>
-    <t>1200 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M19x1750</t>
-  </si>
-  <si>
-    <t>95 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M19x850mm</t>
-  </si>
-  <si>
-    <t>Through Bolt M19x850mm Nut 80Kg</t>
-  </si>
-  <si>
-    <t>Through Bolt M19x850mm Washer 34Kg</t>
-  </si>
-  <si>
-    <t>Through Bolt M20x1350</t>
-  </si>
-  <si>
-    <t>Through Bolt M24X1250mm</t>
-  </si>
-  <si>
-    <t>196 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M24X2300mm</t>
-  </si>
-  <si>
-    <t>Through Bolt M24X850mm</t>
-  </si>
-  <si>
-    <t>330 Nos</t>
-  </si>
-  <si>
-    <t>Through Bolt M30*4000mm</t>
-  </si>
-  <si>
-    <t>Through Bolt M36x1050</t>
-  </si>
-  <si>
-    <t>ThroughBoltM19x700</t>
-  </si>
-  <si>
-    <t>Tieting Machine</t>
-  </si>
-  <si>
-    <t>Toolbox</t>
-  </si>
-  <si>
-    <t>Total Station Machine</t>
-  </si>
-  <si>
-    <t>Tower Cooling</t>
-  </si>
-  <si>
-    <t>Transparent Tape</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 12400mm</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 17.5Ft</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 3.5ft</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 34Ft</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 35Ft</t>
-  </si>
-  <si>
-    <t>Tress For Gantry 600x3800mm</t>
-  </si>
-  <si>
-    <t>Tress For Gantry Jhulla Type</t>
-  </si>
-  <si>
-    <t>Tress For Gantry Small</t>
-  </si>
-  <si>
-    <t>Tress Hook</t>
-  </si>
-  <si>
-    <t>Tripod Stand</t>
-  </si>
-  <si>
-    <t>Troller LWO bed</t>
-  </si>
-  <si>
-    <t>Troller Low Bed</t>
-  </si>
-  <si>
-    <t>Trolley Rehro (Front Part)</t>
-  </si>
-  <si>
-    <t>Trolly Fan</t>
-  </si>
-  <si>
-    <t>Trolly Rehro (front part)</t>
-  </si>
-  <si>
-    <t>Trolly fan 46in</t>
-  </si>
-  <si>
-    <t>4 Set</t>
-  </si>
-  <si>
-    <t>Trowel</t>
-  </si>
-  <si>
-    <t>Trumpet Cone 17/0.5in</t>
-  </si>
-  <si>
-    <t>506 Nos</t>
-  </si>
-  <si>
-    <t>Trumpet Cone 4/0.5in</t>
-  </si>
-  <si>
-    <t>932 Nos</t>
-  </si>
-  <si>
-    <t>Trumpet Large Size</t>
-  </si>
-  <si>
-    <t>Twister Bar</t>
-  </si>
-  <si>
-    <t>90 Nos</t>
-  </si>
-  <si>
-    <t>Tyres and Rims For Welding Generator (Miller)</t>
-  </si>
-  <si>
-    <t>Umbrella Large with Base</t>
-  </si>
-  <si>
-    <t>Underground Valve 25mm</t>
-  </si>
-  <si>
-    <t>Valve 1/2 S.S</t>
-  </si>
-  <si>
-    <t>77 Nos</t>
-  </si>
-  <si>
-    <t>Vibrator Gully</t>
-  </si>
-  <si>
-    <t>Vibrator Motor</t>
-  </si>
-  <si>
-    <t>Vibrator Shaft 50MMx6Mtr</t>
-  </si>
-  <si>
-    <t>Visitor chairs</t>
-  </si>
-  <si>
-    <t>Waher 1.5"X0.5"</t>
-  </si>
-  <si>
-    <t>Warning Tape</t>
-  </si>
-  <si>
-    <t>Washer 20mm</t>
-  </si>
-  <si>
-    <t>Washer 24mm</t>
-  </si>
-  <si>
-    <t>Washer 36mm</t>
-  </si>
-  <si>
-    <t>Washer 3mm</t>
-  </si>
-  <si>
-    <t>Washer 5/8</t>
-  </si>
-  <si>
-    <t>Washer 5mm 3"X3"</t>
-  </si>
-  <si>
-    <t>Washer 6"</t>
-  </si>
-  <si>
-    <t>Washer For T Bolt</t>
-  </si>
-  <si>
-    <t>65 Kg</t>
-  </si>
-  <si>
-    <t>Washer for Dywidag bar</t>
-  </si>
-  <si>
-    <t>23 Nos</t>
-  </si>
-  <si>
-    <t>Washing Machine Haier</t>
-  </si>
-  <si>
-    <t>Water Bowser With Tyres</t>
-  </si>
-  <si>
-    <t>Water Bozzer</t>
-  </si>
-  <si>
-    <t>Water Cooler</t>
-  </si>
-  <si>
-    <t>Water Pump 0.75HP</t>
-  </si>
-  <si>
-    <t>Wax</t>
-  </si>
-  <si>
-    <t>Wedges 0.5"</t>
-  </si>
-  <si>
-    <t>3339 Nos</t>
-  </si>
-  <si>
-    <t>Weight Scale 100Kg</t>
-  </si>
-  <si>
-    <t>Welding Generator (Lincoln)</t>
-  </si>
-  <si>
-    <t>Welding Generator (Miller)</t>
-  </si>
-  <si>
-    <t>Welding Generator Daw-500</t>
-  </si>
-  <si>
-    <t>Welding Generator Lincoln</t>
-  </si>
-  <si>
-    <t>Welding Generator Miller</t>
-  </si>
-  <si>
-    <t>Welding Generator Perkins</t>
-  </si>
-  <si>
-    <t>Welding Glass</t>
-  </si>
-  <si>
-    <t>Welding Gloves</t>
-  </si>
-  <si>
-    <t>Welding Lead</t>
-  </si>
-  <si>
-    <t>20 Rft</t>
-  </si>
-  <si>
-    <t>Welding Plant 3 phase</t>
-  </si>
-  <si>
-    <t>Welding Plant 3Phase 2X400</t>
-  </si>
-  <si>
-    <t>Welding Plant 3Phase 500A with lead</t>
-  </si>
-  <si>
-    <t>Welding Rod 10#</t>
-  </si>
-  <si>
-    <t>80 Pkt</t>
-  </si>
-  <si>
-    <t>Welding Rod 10# (7018)</t>
-  </si>
-  <si>
-    <t>1 Pkt</t>
-  </si>
-  <si>
-    <t>Welding Rod 12#</t>
-  </si>
-  <si>
-    <t>32 Pkt</t>
-  </si>
-  <si>
-    <t>Welding Rod 45&amp;48mm</t>
-  </si>
-  <si>
-    <t>96 Nos</t>
-  </si>
-  <si>
-    <t>Welding Rod 8#</t>
-  </si>
-  <si>
-    <t>14 Pkt</t>
-  </si>
-  <si>
-    <t>Welding Rod Holder 1000A</t>
-  </si>
-  <si>
-    <t>Welding Screen</t>
-  </si>
-  <si>
-    <t>Welding plant single phase</t>
-  </si>
-  <si>
-    <t>Wench</t>
-  </si>
-  <si>
-    <t>Wench Double Drum</t>
-  </si>
-  <si>
-    <t>Wench Roller</t>
-  </si>
-  <si>
-    <t>WiFi USB</t>
-  </si>
-  <si>
-    <t>Wind Pipe</t>
-  </si>
-  <si>
-    <t>Wire Bush</t>
-  </si>
-  <si>
-    <t>Wooden Batten 3inx6inx8ft</t>
-  </si>
-  <si>
-    <t>437 Nos</t>
-  </si>
-  <si>
-    <t>Wooden Batten 4inx8ft</t>
-  </si>
-  <si>
-    <t>269 Nos</t>
-  </si>
-  <si>
-    <t>Wooden Batten 6 1/2ftx1 1/2inx6in</t>
-  </si>
-  <si>
-    <t>70 Nos</t>
-  </si>
-  <si>
-    <t>Wooden Bhatta</t>
-  </si>
-  <si>
-    <t>Wooden Cutting Disc 14"</t>
-  </si>
-  <si>
-    <t>Wooden Garmala</t>
-  </si>
-  <si>
-    <t>Wooden Gutka 18"*18*3ft</t>
-  </si>
-  <si>
-    <t>Wooden Screw 4"</t>
-  </si>
-  <si>
-    <t>Wooden Washers</t>
-  </si>
-  <si>
-    <t>Wooden batten 3"*4"*8ft</t>
-  </si>
-  <si>
-    <t>814 Nos</t>
-  </si>
-  <si>
-    <t>Wooden packen</t>
-  </si>
-  <si>
-    <t>1667 Nos</t>
-  </si>
-  <si>
-    <t>Wooden washer 4"*6"</t>
-  </si>
-  <si>
-    <t>Work Bench Clump 6in</t>
-  </si>
-  <si>
-    <t>Writing pad small</t>
-  </si>
-  <si>
-    <t>pad lock</t>
-  </si>
-  <si>
-    <t>pvc pipe 1inch</t>
-  </si>
-  <si>
-    <t>1045 Nos</t>
-  </si>
-  <si>
-    <t>sheet pipe 81mm</t>
-  </si>
-  <si>
-    <t>591 Nos</t>
-  </si>
-  <si>
-    <t>sheet pipe 84mm</t>
-  </si>
-  <si>
-    <t>122 Nos</t>
-  </si>
-  <si>
     <t>sheet pipe45mm</t>
   </si>
   <si>
-    <t>1248 Nos</t>
+    <t>1146 Nos</t>
   </si>
   <si>
     <t>white cement</t>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Mon Sep 14 2026 09:59:01</t>
+    <t>Date: Tue Sep 15 2026 09:59:05</t>
   </si>
   <si>
     <t/>
@@ -220,7 +220,7 @@
     <t>Binding Wire</t>
   </si>
   <si>
-    <t>367 Kg</t>
+    <t>256 Kg</t>
   </si>
   <si>
     <t>Bit 1.5in for Drill Bil</t>
@@ -583,7 +583,7 @@
     <t>Curing Compound Sika Antisol</t>
   </si>
   <si>
-    <t>170 Drum</t>
+    <t>169 Drum</t>
   </si>
   <si>
     <t>Curing Pipe 1in</t>
@@ -871,7 +871,7 @@
     <t>Foam Sheet 5mm</t>
   </si>
   <si>
-    <t>354 Nos</t>
+    <t>341 Nos</t>
   </si>
   <si>
     <t>Folding Pipe 10ft</t>
@@ -1891,7 +1891,7 @@
     <t>PC Strand Wire</t>
   </si>
   <si>
-    <t>436 Roll</t>
+    <t>435 Roll</t>
   </si>
   <si>
     <t>PPR Elbow 25mm</t>
@@ -1999,7 +1999,7 @@
     <t>PVC Pipe 1-1/4"</t>
   </si>
   <si>
-    <t>404 Nos</t>
+    <t>392 Nos</t>
   </si>
   <si>
     <t>PVC Pipe 150mm</t>
@@ -2155,7 +2155,7 @@
     <t>Plastic Saddle</t>
   </si>
   <si>
-    <t>793 Nos</t>
+    <t>788 Nos</t>
   </si>
   <si>
     <t>Platform For Gantry</t>
@@ -2725,7 +2725,7 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
-    <t>98 Nos</t>
+    <t>88 Nos</t>
   </si>
   <si>
     <t>Sunction Pipe 1.5in</t>
@@ -2917,13 +2917,13 @@
     <t>Trumpet Cone 17/0.5in</t>
   </si>
   <si>
-    <t>479 Nos</t>
+    <t>459 Nos</t>
   </si>
   <si>
     <t>Trumpet Cone 4/0.5in</t>
   </si>
   <si>
-    <t>918 Nos</t>
+    <t>906 Nos</t>
   </si>
   <si>
     <t>Trumpet Large Size</t>
@@ -3022,7 +3022,7 @@
     <t>Wedges 0.5"</t>
   </si>
   <si>
-    <t>2999 Nos</t>
+    <t>2829 Nos</t>
   </si>
   <si>
     <t>Weight Scale 100Kg</t>
@@ -3094,7 +3094,7 @@
     <t>Welding Rod 8#</t>
   </si>
   <si>
-    <t>10 Pkt</t>
+    <t>5 Pkt</t>
   </si>
   <si>
     <t>Welding Rod Holder 1000A</t>
@@ -3187,25 +3187,25 @@
     <t>pvc pipe 1inch</t>
   </si>
   <si>
-    <t>980 Nos</t>
+    <t>947 Nos</t>
   </si>
   <si>
     <t>sheet pipe 81mm</t>
   </si>
   <si>
-    <t>541 Nos</t>
+    <t>1189 Nos</t>
   </si>
   <si>
     <t>sheet pipe 84mm</t>
   </si>
   <si>
-    <t>118 Nos</t>
+    <t>109 Nos</t>
   </si>
   <si>
     <t>sheet pipe45mm</t>
   </si>
   <si>
-    <t>1146 Nos</t>
+    <t>1041 Nos</t>
   </si>
   <si>
     <t>white cement</t>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1064">
   <si>
     <t>KK Girder Project</t>
   </si>
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Sep 15 2026 09:59:05</t>
+    <t>Date: Wed Sep 16 2026 09:59:01</t>
   </si>
   <si>
     <t/>
@@ -220,7 +220,7 @@
     <t>Binding Wire</t>
   </si>
   <si>
-    <t>256 Kg</t>
+    <t>41 Kg</t>
   </si>
   <si>
     <t>Bit 1.5in for Drill Bil</t>
@@ -583,7 +583,7 @@
     <t>Curing Compound Sika Antisol</t>
   </si>
   <si>
-    <t>169 Drum</t>
+    <t>168 Drum</t>
   </si>
   <si>
     <t>Curing Pipe 1in</t>
@@ -871,7 +871,7 @@
     <t>Foam Sheet 5mm</t>
   </si>
   <si>
-    <t>341 Nos</t>
+    <t>330 Nos</t>
   </si>
   <si>
     <t>Folding Pipe 10ft</t>
@@ -1891,7 +1891,7 @@
     <t>PC Strand Wire</t>
   </si>
   <si>
-    <t>435 Roll</t>
+    <t>434 Roll</t>
   </si>
   <si>
     <t>PPR Elbow 25mm</t>
@@ -1999,7 +1999,7 @@
     <t>PVC Pipe 1-1/4"</t>
   </si>
   <si>
-    <t>392 Nos</t>
+    <t>349 Nos</t>
   </si>
   <si>
     <t>PVC Pipe 150mm</t>
@@ -2155,7 +2155,7 @@
     <t>Plastic Saddle</t>
   </si>
   <si>
-    <t>788 Nos</t>
+    <t>778 Nos</t>
   </si>
   <si>
     <t>Platform For Gantry</t>
@@ -2725,9 +2725,6 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
-    <t>88 Nos</t>
-  </si>
-  <si>
     <t>Sunction Pipe 1.5in</t>
   </si>
   <si>
@@ -2833,9 +2830,6 @@
     <t>Through Bolt M24X850mm</t>
   </si>
   <si>
-    <t>330 Nos</t>
-  </si>
-  <si>
     <t>Through Bolt M30*4000mm</t>
   </si>
   <si>
@@ -2917,13 +2911,13 @@
     <t>Trumpet Cone 17/0.5in</t>
   </si>
   <si>
-    <t>459 Nos</t>
+    <t>429 Nos</t>
   </si>
   <si>
     <t>Trumpet Cone 4/0.5in</t>
   </si>
   <si>
-    <t>906 Nos</t>
+    <t>892 Nos</t>
   </si>
   <si>
     <t>Trumpet Large Size</t>
@@ -3022,7 +3016,7 @@
     <t>Wedges 0.5"</t>
   </si>
   <si>
-    <t>2829 Nos</t>
+    <t>2319 Nos</t>
   </si>
   <si>
     <t>Weight Scale 100Kg</t>
@@ -3094,7 +3088,7 @@
     <t>Welding Rod 8#</t>
   </si>
   <si>
-    <t>5 Pkt</t>
+    <t>3 Pkt</t>
   </si>
   <si>
     <t>Welding Rod Holder 1000A</t>
@@ -3187,25 +3181,22 @@
     <t>pvc pipe 1inch</t>
   </si>
   <si>
-    <t>947 Nos</t>
+    <t>887 Nos</t>
   </si>
   <si>
     <t>sheet pipe 81mm</t>
   </si>
   <si>
-    <t>1189 Nos</t>
+    <t>1624 Nos</t>
   </si>
   <si>
     <t>sheet pipe 84mm</t>
   </si>
   <si>
-    <t>109 Nos</t>
-  </si>
-  <si>
     <t>sheet pipe45mm</t>
   </si>
   <si>
-    <t>1041 Nos</t>
+    <t>937 Nos</t>
   </si>
   <si>
     <t>white cement</t>
@@ -13550,7 +13541,7 @@
         <v>9</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>904</v>
+        <v>520</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
@@ -13558,13 +13549,13 @@
         <v>707</v>
       </c>
       <c r="B712" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D712" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="C712" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D712" s="2" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
@@ -13572,7 +13563,7 @@
         <v>708</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>9</v>
@@ -13586,7 +13577,7 @@
         <v>709</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>9</v>
@@ -13600,7 +13591,7 @@
         <v>710</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>9</v>
@@ -13614,7 +13605,7 @@
         <v>711</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>9</v>
@@ -13628,13 +13619,13 @@
         <v>712</v>
       </c>
       <c r="B717" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C717" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D717" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="C717" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D717" s="2" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
@@ -13642,7 +13633,7 @@
         <v>713</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>9</v>
@@ -13656,7 +13647,7 @@
         <v>714</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>9</v>
@@ -13670,7 +13661,7 @@
         <v>715</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>9</v>
@@ -13684,7 +13675,7 @@
         <v>716</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>9</v>
@@ -13698,13 +13689,13 @@
         <v>717</v>
       </c>
       <c r="B722" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D722" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="C722" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D722" s="2" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
@@ -13712,13 +13703,13 @@
         <v>718</v>
       </c>
       <c r="B723" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D723" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="C723" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D723" s="2" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
@@ -13726,13 +13717,13 @@
         <v>719</v>
       </c>
       <c r="B724" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D724" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="C724" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D724" s="2" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
@@ -13740,7 +13731,7 @@
         <v>720</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>9</v>
@@ -13754,13 +13745,13 @@
         <v>721</v>
       </c>
       <c r="B726" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D726" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="C726" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D726" s="2" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
@@ -13768,13 +13759,13 @@
         <v>722</v>
       </c>
       <c r="B727" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D727" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="C727" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D727" s="2" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
@@ -13782,13 +13773,13 @@
         <v>723</v>
       </c>
       <c r="B728" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D728" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="C728" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D728" s="2" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
@@ -13796,13 +13787,13 @@
         <v>724</v>
       </c>
       <c r="B729" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D729" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="C729" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D729" s="2" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
@@ -13810,13 +13801,13 @@
         <v>725</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D730" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
@@ -13824,7 +13815,7 @@
         <v>726</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>9</v>
@@ -13838,7 +13829,7 @@
         <v>727</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>9</v>
@@ -13852,7 +13843,7 @@
         <v>728</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>9</v>
@@ -13866,13 +13857,13 @@
         <v>729</v>
       </c>
       <c r="B734" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C734" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D734" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="C734" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D734" s="2" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
@@ -13880,7 +13871,7 @@
         <v>730</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>9</v>
@@ -13894,13 +13885,13 @@
         <v>731</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D736" s="2" t="s">
-        <v>940</v>
+        <v>286</v>
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
@@ -13908,7 +13899,7 @@
         <v>732</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>9</v>
@@ -13922,7 +13913,7 @@
         <v>733</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>9</v>
@@ -13936,7 +13927,7 @@
         <v>734</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>9</v>
@@ -13950,7 +13941,7 @@
         <v>735</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>9</v>
@@ -13964,7 +13955,7 @@
         <v>736</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>9</v>
@@ -13978,7 +13969,7 @@
         <v>737</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>9</v>
@@ -13992,7 +13983,7 @@
         <v>738</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>9</v>
@@ -14006,7 +13997,7 @@
         <v>739</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>9</v>
@@ -14020,7 +14011,7 @@
         <v>740</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>9</v>
@@ -14034,7 +14025,7 @@
         <v>741</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>9</v>
@@ -14048,7 +14039,7 @@
         <v>742</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>9</v>
@@ -14062,7 +14053,7 @@
         <v>743</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>9</v>
@@ -14076,7 +14067,7 @@
         <v>744</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>9</v>
@@ -14090,7 +14081,7 @@
         <v>745</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>9</v>
@@ -14104,7 +14095,7 @@
         <v>746</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>9</v>
@@ -14118,7 +14109,7 @@
         <v>747</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>9</v>
@@ -14132,7 +14123,7 @@
         <v>748</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>9</v>
@@ -14146,7 +14137,7 @@
         <v>749</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>9</v>
@@ -14160,7 +14151,7 @@
         <v>750</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>9</v>
@@ -14174,7 +14165,7 @@
         <v>751</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>9</v>
@@ -14188,7 +14179,7 @@
         <v>752</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>9</v>
@@ -14202,7 +14193,7 @@
         <v>753</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>9</v>
@@ -14216,7 +14207,7 @@
         <v>754</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>9</v>
@@ -14230,13 +14221,13 @@
         <v>755</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D760" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
@@ -14244,7 +14235,7 @@
         <v>756</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>9</v>
@@ -14258,13 +14249,13 @@
         <v>757</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D762" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
@@ -14272,13 +14263,13 @@
         <v>758</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D763" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
@@ -14286,7 +14277,7 @@
         <v>759</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>9</v>
@@ -14300,13 +14291,13 @@
         <v>760</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D765" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
@@ -14314,7 +14305,7 @@
         <v>761</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>9</v>
@@ -14328,7 +14319,7 @@
         <v>762</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>9</v>
@@ -14342,7 +14333,7 @@
         <v>763</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>9</v>
@@ -14356,13 +14347,13 @@
         <v>764</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
@@ -14370,7 +14361,7 @@
         <v>765</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>9</v>
@@ -14384,7 +14375,7 @@
         <v>766</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>9</v>
@@ -14398,7 +14389,7 @@
         <v>767</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>9</v>
@@ -14412,7 +14403,7 @@
         <v>768</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>9</v>
@@ -14426,7 +14417,7 @@
         <v>769</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>9</v>
@@ -14440,7 +14431,7 @@
         <v>770</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>9</v>
@@ -14454,7 +14445,7 @@
         <v>771</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>9</v>
@@ -14468,7 +14459,7 @@
         <v>772</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>9</v>
@@ -14482,7 +14473,7 @@
         <v>773</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>9</v>
@@ -14496,7 +14487,7 @@
         <v>774</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>9</v>
@@ -14510,7 +14501,7 @@
         <v>775</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>9</v>
@@ -14524,7 +14515,7 @@
         <v>776</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>9</v>
@@ -14538,7 +14529,7 @@
         <v>777</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>9</v>
@@ -14552,13 +14543,13 @@
         <v>778</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.25">
@@ -14566,13 +14557,13 @@
         <v>779</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D784" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.25">
@@ -14580,7 +14571,7 @@
         <v>780</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>9</v>
@@ -14594,7 +14585,7 @@
         <v>781</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>9</v>
@@ -14608,7 +14599,7 @@
         <v>782</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>9</v>
@@ -14622,7 +14613,7 @@
         <v>783</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>9</v>
@@ -14636,7 +14627,7 @@
         <v>784</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>9</v>
@@ -14650,7 +14641,7 @@
         <v>785</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>9</v>
@@ -14664,13 +14655,13 @@
         <v>786</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.25">
@@ -14678,7 +14669,7 @@
         <v>787</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>9</v>
@@ -14692,7 +14683,7 @@
         <v>788</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>9</v>
@@ -14706,7 +14697,7 @@
         <v>789</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>9</v>
@@ -14720,7 +14711,7 @@
         <v>790</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>9</v>
@@ -14734,7 +14725,7 @@
         <v>791</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>9</v>
@@ -14748,7 +14739,7 @@
         <v>792</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>9</v>
@@ -14762,7 +14753,7 @@
         <v>793</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>9</v>
@@ -14776,7 +14767,7 @@
         <v>794</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>9</v>
@@ -14790,7 +14781,7 @@
         <v>795</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>9</v>
@@ -14804,13 +14795,13 @@
         <v>796</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D801" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.25">
@@ -14818,7 +14809,7 @@
         <v>797</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>9</v>
@@ -14832,7 +14823,7 @@
         <v>798</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>9</v>
@@ -14846,7 +14837,7 @@
         <v>799</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>9</v>
@@ -14860,13 +14851,13 @@
         <v>800</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.25">
@@ -14874,13 +14865,13 @@
         <v>801</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D806" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.25">
@@ -14888,13 +14879,13 @@
         <v>802</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.25">
@@ -14902,13 +14893,13 @@
         <v>803</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D808" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.25">
@@ -14916,13 +14907,13 @@
         <v>804</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.25">
@@ -14930,7 +14921,7 @@
         <v>805</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>9</v>
@@ -14944,7 +14935,7 @@
         <v>806</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>9</v>
@@ -14958,7 +14949,7 @@
         <v>807</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>9</v>
@@ -14972,7 +14963,7 @@
         <v>808</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>9</v>
@@ -14986,7 +14977,7 @@
         <v>809</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>9</v>
@@ -15000,7 +14991,7 @@
         <v>810</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>9</v>
@@ -15014,7 +15005,7 @@
         <v>811</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>9</v>
@@ -15028,7 +15019,7 @@
         <v>812</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>9</v>
@@ -15042,7 +15033,7 @@
         <v>813</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>9</v>
@@ -15056,13 +15047,13 @@
         <v>814</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C819" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D819" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
@@ -15070,13 +15061,13 @@
         <v>815</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C820" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
@@ -15084,13 +15075,13 @@
         <v>816</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C821" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
@@ -15098,7 +15089,7 @@
         <v>817</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>9</v>
@@ -15112,7 +15103,7 @@
         <v>818</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>9</v>
@@ -15126,7 +15117,7 @@
         <v>819</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C824" s="2" t="s">
         <v>9</v>
@@ -15140,7 +15131,7 @@
         <v>820</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>9</v>
@@ -15154,7 +15145,7 @@
         <v>821</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C826" s="2" t="s">
         <v>9</v>
@@ -15168,7 +15159,7 @@
         <v>822</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>9</v>
@@ -15182,13 +15173,13 @@
         <v>823</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C828" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.25">
@@ -15196,13 +15187,13 @@
         <v>824</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D829" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
@@ -15210,13 +15201,13 @@
         <v>825</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
@@ -15224,7 +15215,7 @@
         <v>826</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>9</v>
@@ -15238,7 +15229,7 @@
         <v>827</v>
       </c>
       <c r="B832" s="2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>9</v>
@@ -15252,7 +15243,7 @@
         <v>828</v>
       </c>
       <c r="B833" s="2" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C833" s="2" t="s">
         <v>9</v>
@@ -15266,13 +15257,13 @@
         <v>829</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D834" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.25">
@@ -15280,13 +15271,13 @@
         <v>830</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.25">
@@ -15294,13 +15285,13 @@
         <v>831</v>
       </c>
       <c r="B836" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>1062</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.25">
@@ -15308,13 +15299,13 @@
         <v>832</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.25">
@@ -15322,13 +15313,13 @@
         <v>833</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Sep 16 2026 09:59:01</t>
+    <t>Date: Thu Sep 17 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Sep 17 2026 09:59:01</t>
+    <t>Date: Fri Sep 18 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Sep 18 2026 09:59:01</t>
+    <t>Date: Sat Sep 19 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Sep 20 2026 09:59:01</t>
+    <t>Date: Tue Sep 22 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Sep 22 2026 09:59:01</t>
+    <t>Date: Wed Sep 23 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Sep 23 2026 09:59:01</t>
+    <t>Date: Thu Sep 24 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Sep 24 2026 09:59:01</t>
+    <t>Date: Fri Sep 25 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Sep 25 2026 09:59:01</t>
+    <t>Date: Sat Sep 26 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sat Sep 26 2026 09:59:01</t>
+    <t>Date: Sun Sep 27 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Sep 27 2026 09:59:01</t>
+    <t>Date: Mon Sep 28 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Mon Sep 28 2026 09:59:01</t>
+    <t>Date: Tue Sep 29 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Sep 29 2026 09:59:01</t>
+    <t>Date: Wed Sep 30 2026 09:59:02</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Sep 30 2026 09:59:02</t>
+    <t>Date: Thu Oct 01 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Oct 01 2026 09:59:01</t>
+    <t>Date: Fri Oct 02 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Oct 02 2026 09:59:01</t>
+    <t>Date: Sat Oct 03 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sat Oct 03 2026 09:59:01</t>
+    <t>Date: Sun Oct 04 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Oct 04 2026 09:59:01</t>
+    <t>Date: Mon Oct 05 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Mon Oct 05 2026 09:59:01</t>
+    <t>Date: Tue Oct 06 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Oct 06 2026 09:59:01</t>
+    <t>Date: Tue Oct 06 2026 19:49:34</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Oct 06 2026 19:49:34</t>
+    <t>Date: Wed Oct 07 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Oct 07 2026 09:59:01</t>
+    <t>Date: Sat Oct 17 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sat Oct 17 2026 09:59:01</t>
+    <t>Date: Sun Oct 18 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Oct 18 2026 09:59:01</t>
+    <t>Date: Mon Oct 19 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Mon Oct 19 2026 09:59:01</t>
+    <t>Date: Tue Oct 20 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Oct 20 2026 09:59:01</t>
+    <t>Date: Wed Oct 21 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Oct 21 2026 09:59:01</t>
+    <t>Date: Thu Oct 22 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Oct 22 2026 09:59:01</t>
+    <t>Date: Fri Oct 23 2026 09:59:02</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Oct 23 2026 09:59:02</t>
+    <t>Date: Sat Oct 24 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sat Oct 24 2026 09:59:01</t>
+    <t>Date: Sun Oct 25 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Sun Oct 25 2026 09:59:01</t>
+    <t>Date: Mon Oct 26 2026 09:59:02</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Mon Oct 26 2026 09:59:02</t>
+    <t>Date: Tue Oct 27 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Tue Oct 27 2026 09:59:01</t>
+    <t>Date: Wed Oct 28 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Oct 28 2026 09:59:01</t>
+    <t>Date: Thu Oct 29 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Oct 29 2026 09:59:01</t>
+    <t>Date: Fri Oct 30 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Oct 30 2026 09:59:01</t>
+    <t>Date: Sat Oct 31 2026 09:59:01</t>
   </si>
   <si>
     <t/>
